--- a/Files/Madden26/IE/Season2/WaiverClaims.xlsx
+++ b/Files/Madden26/IE/Season2/WaiverClaims.xlsx
@@ -479,7 +479,7 @@
         <v>0.15</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         <v>0.15</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -614,7 +614,7 @@
         <v>0.15</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>0.15</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>0.1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -772,7 +772,7 @@
         <v>0.15</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>0.1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -992,7 +992,7 @@
         <v>0.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
@@ -1046,7 +1046,7 @@
         <v>0.1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
@@ -1177,7 +1177,7 @@
         <v>0.1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
         <v>0.1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
@@ -1273,7 +1273,7 @@
         <v>0.1</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
